--- a/data/credit_bond_2026-07-22.xlsx
+++ b/data/credit_bond_2026-07-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-22" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-23" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,6 +37,10 @@
       <sz val="12.0"/>
       <color indexed="8"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="12.0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -90,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -99,6 +103,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -149,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY1"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -163,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-22</t>
+          <t>数据来源：DM    2026-07-23</t>
         </is>
       </c>
     </row>
@@ -667,6 +677,876 @@
         <is>
           <t>团费(%)</t>
         </is>
+      </c>
+    </row>
+    <row r="3" customHeight="true" ht="18.0">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>26恒丰银行绿债01B</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1.35 ~ 1.85</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>25恒丰银行债02</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>1.83Y</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>1.5832</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>07-23 09:00</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-27</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AY3" s="3"/>
+    </row>
+    <row r="4" customHeight="true" ht="18.0">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>26长开G1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>245671.SH</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>24长寿开投MTN003A</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>1.10Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>1.7196</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>重庆长寿开发投资(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>07-23 15:00</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>a-</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>重庆市-长寿区</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还回售的公司债券本金[23长开04]</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>国投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2027-07-28</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AY4" s="3"/>
+    </row>
+    <row r="5" customHeight="true" ht="18.0">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>26恒丰银行绿债01A</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>25恒丰银行债02</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>1.83Y</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>1.5832</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>07-23 09:00</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-27</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AY5" s="3"/>
+    </row>
+    <row r="6" customHeight="true" ht="18.0">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>26成都开投PPN001</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>5+5</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>25成都开投PPN002</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>4.31Y+5.00Y</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2.1942</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>成都经开国投集团有限公司</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>07-23 09:00</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>四川省-成都市</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>本次定向债务融资工具注册金额为20亿元,本期发行金额为13亿元,募集资金均用于偿还发行人存量债务融资工具本金；本期募集资金13亿元用于置换上述银行贷款本金[23成都国投PPN001]</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司,成都银行股份有限公司,国投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>成都经开国投集团有限公司2026年度第一期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>2036-07-24</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2031-07-24</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AY6" s="4" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/data/credit_bond_2026-07-22.xlsx
+++ b/data/credit_bond_2026-07-22.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6050/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.7100</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6050/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">

--- a/data/credit_bond_2026-07-22.xlsx
+++ b/data/credit_bond_2026-07-22.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.6050/--</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.6050/--</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">

--- a/data/credit_bond_2026-07-22.xlsx
+++ b/data/credit_bond_2026-07-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-23" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-24" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>07-23 18:00</t>
+          <t>07-23 19:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -928,8 +928,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>56.28</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -952,7 +956,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7100</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1421,7 +1425,11 @@
           <t>aa序列</t>
         </is>
       </c>
-      <c r="W6" s="3"/>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>2.21%~2.31%</t>
+        </is>
+      </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
           <t>AA+</t>

--- a/data/credit_bond_2026-07-22.xlsx
+++ b/data/credit_bond_2026-07-22.xlsx
@@ -1366,8 +1366,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>51.75</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -1413,7 +1417,9 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="S6" s="3"/>
+      <c r="S6" s="4" t="n">
+        <v>3.58</v>
+      </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_2026-07-22.xlsx
+++ b/data/credit_bond_2026-07-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-24" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-27" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-24</t>
+          <t>数据来源：DM    2026-07-27</t>
         </is>
       </c>
     </row>
@@ -682,59 +682,67 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26恒丰银行绿债01B</t>
+          <t>26长开G1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>07-23 18:00</t>
-        </is>
-      </c>
-      <c r="C3" s="3"/>
+          <t>07-23 19:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>245671.SH</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.85</t>
-        </is>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>56.28</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25恒丰银行债02</t>
+          <t>24长寿开投MTN003A</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>1.83Y</t>
+          <t>1.10Y+2.00Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.5832</t>
+          <t>1.7196</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.5900/--</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司</t>
+          <t>重庆长寿开发投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -744,7 +752,7 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>07-23 09:00</t>
+          <t>07-23 15:00</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -756,48 +764,44 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>aa序列</t>
+          <t>a-</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y3" s="3"/>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>重庆市-长寿区</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
+          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还回售的公司债券本金[23长开04]</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
+          <t>国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr">
@@ -807,12 +811,12 @@
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
@@ -822,7 +826,7 @@
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>2029-07-27</t>
+          <t>2027-07-28</t>
         </is>
       </c>
       <c r="AJ3" s="3"/>
@@ -833,7 +837,7 @@
       </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -843,32 +847,32 @@
       </c>
       <c r="AN3" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
@@ -901,67 +905,69 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26长开G1</t>
+          <t>26恒丰银行绿债01A</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>07-23 19:00</t>
+          <t>07-23 18:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>245671.SH</t>
+          <t>222680006.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>55.0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>55.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>56.28</v>
+        <v>27.42</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>24长寿开投MTN003A</t>
+          <t>25恒丰银行债02</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>1.10Y+2.00Y</t>
+          <t>1.83Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.7196</t>
+          <t>1.5832</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.7300/--</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司</t>
+          <t>恒丰银行股份有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -971,7 +977,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>07-23 15:00</t>
+          <t>07-23 09:00</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -983,44 +989,48 @@
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>a-</t>
+          <t>aa序列</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Y4" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>重庆市-长寿区</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还回售的公司债券本金[23长开04]</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
@@ -1030,12 +1040,12 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
@@ -1045,7 +1055,7 @@
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>2027-07-28</t>
+          <t>2029-07-27</t>
         </is>
       </c>
       <c r="AJ4" s="3"/>
@@ -1056,7 +1066,7 @@
       </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1066,32 +1076,32 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
@@ -1124,7 +1134,7 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26恒丰银行绿债01A</t>
+          <t>26恒丰银行绿债01B</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1132,23 +1142,33 @@
           <t>07-23 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>222680007.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>25.0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>25.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+          <t>1.35 ~ 1.85</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>31.42</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.63</t>
@@ -1254,7 +1274,7 @@
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
@@ -1351,7 +1371,11 @@
           <t>07-23 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>032601649.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>5+5</t>
@@ -1360,7 +1384,9 @@
       <c r="E6" s="4" t="n">
         <v>13.0</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="n">
+        <v>13.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>1.80 ~ 2.80</t>
@@ -1418,7 +1444,7 @@
         </is>
       </c>
       <c r="S6" s="4" t="n">
-        <v>3.58</v>
+        <v>3.5846</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3" t="inlineStr">
@@ -1562,6 +1588,229 @@
       <c r="AY6" s="4" t="n">
         <v>0.01</v>
       </c>
+    </row>
+    <row r="7" customHeight="true" ht="18.0">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>26鸿飞02</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>07-27 18:00</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>283448.SH</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>26鸿飞01</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>4.67Y</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2.2952</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>江油鸿飞投资(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>07-27 15:00</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>a+</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>2.03%~2.13%</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>四川省-绵阳市</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>本次公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券23江油02的本金[23江油02]</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>长城证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>四川省金玉融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>江油鸿飞投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>2031-07-28</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AY7" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-07-22.xlsx
+++ b/data/credit_bond_2026-07-22.xlsx
@@ -703,7 +703,9 @@
       <c r="E3" s="4" t="n">
         <v>2.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 2.40</t>
@@ -760,7 +762,9 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="S3" s="3"/>
+      <c r="S3" s="4" t="n">
+        <v>2.7</v>
+      </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
@@ -1061,7 +1065,7 @@
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AL4" s="3" t="inlineStr">
@@ -1290,7 +1294,7 @@
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AL5" s="3" t="inlineStr">
@@ -1597,7 +1601,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>07-27 18:00</t>
+          <t>07-27 19:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1638,7 +1642,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2.2952</t>
+          <t>2.2945</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">

--- a/data/credit_bond_2026-07-22.xlsx
+++ b/data/credit_bond_2026-07-22.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-27" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,9 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>2.34</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
